--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008520536396819937</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48092402</v>
+        <v>4030140</v>
       </c>
       <c r="L2" t="n">
-        <v>25256666</v>
+        <v>1620684</v>
       </c>
       <c r="M2" t="n">
-        <v>5929910</v>
+        <v>299998</v>
       </c>
       <c r="N2" t="n">
-        <v>273806</v>
+        <v>6933</v>
       </c>
       <c r="O2" t="n">
-        <v>3504750</v>
+        <v>189709</v>
       </c>
       <c r="P2" t="n">
-        <v>1276173</v>
+        <v>30669</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999684691429138</v>
+        <v>0.9998980760574341</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8338537812232971</v>
+        <v>0.7138895392417908</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7038031220436096</v>
+        <v>0.5302372574806213</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6296451687812805</v>
+        <v>0.4004511833190918</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2711508870124817</v>
+        <v>0.05642595142126083</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6744852066040039</v>
+        <v>0.4263286590576172</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8082476854324341</v>
+        <v>0.6119358539581299</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039522590464157</v>
       </c>
       <c r="C3" t="n">
-        <v>275</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n">
-        <v>48092402</v>
+        <v>4030140</v>
       </c>
       <c r="E3" t="n">
-        <v>7087382</v>
+        <v>907838</v>
       </c>
       <c r="F3" t="n">
-        <v>219275</v>
+        <v>42142</v>
       </c>
       <c r="G3" t="n">
-        <v>18401</v>
+        <v>3753</v>
       </c>
       <c r="H3" t="n">
-        <v>16027</v>
+        <v>4607</v>
       </c>
       <c r="I3" t="n">
-        <v>815</v>
+        <v>147</v>
       </c>
       <c r="J3" t="n">
-        <v>110763619</v>
+        <v>10068973</v>
       </c>
       <c r="K3" t="n">
-        <v>115558963</v>
+        <v>9812099</v>
       </c>
       <c r="L3" t="n">
-        <v>133653458</v>
+        <v>11640252</v>
       </c>
       <c r="M3" t="n">
-        <v>166778192</v>
+        <v>15022465</v>
       </c>
       <c r="N3" t="n">
-        <v>178854559</v>
+        <v>16209957</v>
       </c>
       <c r="O3" t="n">
-        <v>173270406</v>
+        <v>15648148</v>
       </c>
       <c r="P3" t="n">
-        <v>178144690</v>
+        <v>16202619</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8675524592399597</v>
+        <v>0.8078514933586121</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6959058046340942</v>
+        <v>0.4852483868598938</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5751689076423645</v>
+        <v>0.3176656067371368</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2778472900390625</v>
+        <v>0.07694185525178909</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6242698431015015</v>
+        <v>0.3701075613498688</v>
       </c>
       <c r="W3" t="n">
-        <v>0.599551796913147</v>
+        <v>0.1581430584192276</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03216441684267991</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>8829050</v>
+        <v>1441471</v>
       </c>
       <c r="E4" t="n">
-        <v>25256666</v>
+        <v>1620684</v>
       </c>
       <c r="F4" t="n">
-        <v>1865158</v>
+        <v>215117</v>
       </c>
       <c r="G4" t="n">
-        <v>107949</v>
+        <v>20688</v>
       </c>
       <c r="H4" t="n">
-        <v>217960</v>
+        <v>40086</v>
       </c>
       <c r="I4" t="n">
-        <v>16347</v>
+        <v>1814</v>
       </c>
       <c r="J4" t="n">
-        <v>2201</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>9582460</v>
+        <v>1615187</v>
       </c>
       <c r="L4" t="n">
-        <v>10629316</v>
+        <v>1435842</v>
       </c>
       <c r="M4" t="n">
-        <v>3487950</v>
+        <v>449152</v>
       </c>
       <c r="N4" t="n">
-        <v>735986</v>
+        <v>115936</v>
       </c>
       <c r="O4" t="n">
-        <v>1691435</v>
+        <v>255274</v>
       </c>
       <c r="P4" t="n">
-        <v>302765</v>
+        <v>19449</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999842047691345</v>
+        <v>0.999949038028717</v>
       </c>
       <c r="R4" t="n">
-        <v>0.850369393825531</v>
+        <v>0.7579696178436279</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6998321413993835</v>
+        <v>0.506746232509613</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6011754870414734</v>
+        <v>0.3542866110801697</v>
       </c>
       <c r="U4" t="n">
-        <v>0.274458259344101</v>
+        <v>0.06510592997074127</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6484067440032959</v>
+        <v>0.3962337672710419</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6884309649467468</v>
+        <v>0.2513337433338165</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="D5" t="n">
-        <v>539748</v>
+        <v>128941</v>
       </c>
       <c r="E5" t="n">
-        <v>2834351</v>
+        <v>388786</v>
       </c>
       <c r="F5" t="n">
-        <v>5929910</v>
+        <v>299998</v>
       </c>
       <c r="G5" t="n">
-        <v>228517</v>
+        <v>32518</v>
       </c>
       <c r="H5" t="n">
-        <v>712622</v>
+        <v>88060</v>
       </c>
       <c r="I5" t="n">
-        <v>64477</v>
+        <v>5991</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7342175</v>
+        <v>958574</v>
       </c>
       <c r="L5" t="n">
-        <v>11036560</v>
+        <v>1719222</v>
       </c>
       <c r="M5" t="n">
-        <v>4379948</v>
+        <v>644385</v>
       </c>
       <c r="N5" t="n">
-        <v>711649</v>
+        <v>83174</v>
       </c>
       <c r="O5" t="n">
-        <v>2109409</v>
+        <v>322869</v>
       </c>
       <c r="P5" t="n">
-        <v>852372</v>
+        <v>163263</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999878406524658</v>
+        <v>0.9999606013298035</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9062741994857788</v>
+        <v>0.8432163000106812</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8800179362297058</v>
+        <v>0.8078055381774902</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9564288854598999</v>
+        <v>0.9333859086036682</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919832348823547</v>
+        <v>0.987870991230011</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9789515733718872</v>
+        <v>0.9647817611694336</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936030507087708</v>
+        <v>0.9888699054718018</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="D6" t="n">
-        <v>158353</v>
+        <v>23505</v>
       </c>
       <c r="E6" t="n">
-        <v>217858</v>
+        <v>27155</v>
       </c>
       <c r="F6" t="n">
-        <v>230447</v>
+        <v>22362</v>
       </c>
       <c r="G6" t="n">
-        <v>273806</v>
+        <v>6933</v>
       </c>
       <c r="H6" t="n">
-        <v>94813</v>
+        <v>9411</v>
       </c>
       <c r="I6" t="n">
-        <v>9863</v>
+        <v>671</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="D7" t="n">
-        <v>52120</v>
+        <v>19659</v>
       </c>
       <c r="E7" t="n">
-        <v>444755</v>
+        <v>99340</v>
       </c>
       <c r="F7" t="n">
-        <v>1067917</v>
+        <v>145088</v>
       </c>
       <c r="G7" t="n">
-        <v>332957</v>
+        <v>47818</v>
       </c>
       <c r="H7" t="n">
-        <v>3504750</v>
+        <v>189709</v>
       </c>
       <c r="I7" t="n">
-        <v>211263</v>
+        <v>10826</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>885</v>
+        <v>217</v>
       </c>
       <c r="D8" t="n">
-        <v>3189</v>
+        <v>1611</v>
       </c>
       <c r="E8" t="n">
-        <v>44970</v>
+        <v>12723</v>
       </c>
       <c r="F8" t="n">
-        <v>105153</v>
+        <v>24443</v>
       </c>
       <c r="G8" t="n">
-        <v>48162</v>
+        <v>11159</v>
       </c>
       <c r="H8" t="n">
-        <v>650013</v>
+        <v>113110</v>
       </c>
       <c r="I8" t="n">
-        <v>1276173</v>
+        <v>30669</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
